--- a/data/env_test/case_excle/GovermentPurchars/case_data_zz.xlsx
+++ b/data/env_test/case_excle/GovermentPurchars/case_data_zz.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\interfaceAutomatic-main\data\env_test\case_excle\GovermentPurchars\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Lucas/PycharmProjects/InterfaceAutomaticTesttPlatform/data/env_test/case_excle/GovermentPurchars/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{401E44B9-C578-400B-8FD0-AF9D940F72A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EE620D-22D7-7B4F-9E9C-659889E17ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="20320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="公开" sheetId="10" r:id="rId1"/>
@@ -580,7 +580,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -631,6 +631,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1155,24 +1156,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="16.375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="45" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.375" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.75" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="2" customWidth="1"/>
+    <col min="7" max="8" width="11.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="53" style="2" customWidth="1"/>
-    <col min="11" max="11" width="26.125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="26.1640625" style="2" customWidth="1"/>
     <col min="12" max="12" width="35" style="2" customWidth="1"/>
-    <col min="13" max="13" width="45.625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="45.6640625" style="2" customWidth="1"/>
     <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="18">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1216,7 +1217,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1245,7 +1246,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -1277,7 +1278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>61</v>
       </c>
@@ -1309,7 +1310,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>62</v>
       </c>
@@ -1338,7 +1339,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>63</v>
       </c>
@@ -1367,7 +1368,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>64</v>
       </c>
@@ -1399,7 +1400,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="346.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="360">
       <c r="A8" s="1" t="s">
         <v>65</v>
       </c>
@@ -1432,7 +1433,7 @@
       </c>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="115.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="126">
       <c r="A9" s="1" t="s">
         <v>98</v>
       </c>
@@ -1463,7 +1464,7 @@
       </c>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="90">
       <c r="A10" s="1" t="s">
         <v>99</v>
       </c>
@@ -1497,7 +1498,7 @@
       </c>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="409.6">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -1526,7 +1527,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="247.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="252">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
@@ -1561,7 +1562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="90">
       <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
@@ -1590,7 +1591,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="90">
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
@@ -1619,7 +1620,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="90">
       <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
@@ -1648,7 +1649,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="90">
       <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
@@ -1677,7 +1678,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="90">
       <c r="A17" s="1" t="s">
         <v>37</v>
       </c>
@@ -1706,7 +1707,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="90">
       <c r="A18" s="1" t="s">
         <v>38</v>
       </c>
@@ -1735,7 +1736,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="90">
       <c r="A19" s="1" t="s">
         <v>39</v>
       </c>
@@ -1764,7 +1765,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
@@ -1793,7 +1794,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="409.6">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
@@ -1822,7 +1823,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="90">
       <c r="A22" s="1" t="s">
         <v>110</v>
       </c>
@@ -1857,7 +1858,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>111</v>
       </c>
@@ -1889,7 +1890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="90">
       <c r="A24" s="1" t="s">
         <v>42</v>
       </c>
@@ -1921,19 +1922,19 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="E2:E24">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
       <formula>"P4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
       <formula>"P3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
       <formula>"P2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1963,24 +1964,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3DF6D78-2EA9-0D4D-A8F7-EC937ACEC0C7}">
   <dimension ref="A1:N27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="16.375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="45" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.375" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.75" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="2" customWidth="1"/>
+    <col min="7" max="8" width="11.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="53" style="2" customWidth="1"/>
-    <col min="11" max="11" width="26.125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="26.1640625" style="2" customWidth="1"/>
     <col min="12" max="12" width="35" style="2" customWidth="1"/>
-    <col min="13" max="13" width="45.625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="45.6640625" style="2" customWidth="1"/>
     <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="18">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2024,7 +2025,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>127</v>
       </c>
@@ -2053,7 +2054,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>128</v>
       </c>
@@ -2085,7 +2086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>129</v>
       </c>
@@ -2117,7 +2118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>130</v>
       </c>
@@ -2146,7 +2147,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>131</v>
       </c>
@@ -2175,7 +2176,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>132</v>
       </c>
@@ -2207,7 +2208,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="346.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="360">
       <c r="A8" s="1" t="s">
         <v>133</v>
       </c>
@@ -2240,7 +2241,7 @@
       </c>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="115.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="126">
       <c r="A9" s="1" t="s">
         <v>134</v>
       </c>
@@ -2271,7 +2272,7 @@
       </c>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="90">
       <c r="A10" s="1" t="s">
         <v>135</v>
       </c>
@@ -2305,7 +2306,7 @@
       </c>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="409.6">
       <c r="A11" s="1" t="s">
         <v>136</v>
       </c>
@@ -2334,7 +2335,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="247.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="252">
       <c r="A12" s="1" t="s">
         <v>137</v>
       </c>
@@ -2369,7 +2370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="90">
       <c r="A13" s="1" t="s">
         <v>138</v>
       </c>
@@ -2398,7 +2399,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="90">
       <c r="A14" s="1" t="s">
         <v>139</v>
       </c>
@@ -2427,7 +2428,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="90">
       <c r="A15" s="1" t="s">
         <v>140</v>
       </c>
@@ -2456,7 +2457,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="90">
       <c r="A16" s="1" t="s">
         <v>141</v>
       </c>
@@ -2485,7 +2486,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="90">
       <c r="A17" s="1" t="s">
         <v>142</v>
       </c>
@@ -2514,7 +2515,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="90">
       <c r="A18" s="1" t="s">
         <v>143</v>
       </c>
@@ -2543,7 +2544,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="90">
       <c r="A19" s="1" t="s">
         <v>144</v>
       </c>
@@ -2572,7 +2573,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>145</v>
       </c>
@@ -2601,7 +2602,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="409.6">
       <c r="A21" s="1" t="s">
         <v>146</v>
       </c>
@@ -2630,7 +2631,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="90">
       <c r="A22" s="1" t="s">
         <v>147</v>
       </c>
@@ -2665,7 +2666,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>148</v>
       </c>
@@ -2697,7 +2698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>149</v>
       </c>
@@ -2726,7 +2727,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="90">
       <c r="A25" s="1" t="s">
         <v>150</v>
       </c>
@@ -2761,7 +2762,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>151</v>
       </c>
@@ -2793,7 +2794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="90">
       <c r="A27" s="1" t="s">
         <v>152</v>
       </c>
@@ -2825,19 +2826,19 @@
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="E2:E27">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"P4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"P3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
       <formula>"P2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2867,24 +2868,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89098C1A-F74A-A24B-BCE4-B3BC9F558B9F}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="16.375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="45" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.375" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.75" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="2" customWidth="1"/>
+    <col min="7" max="8" width="11.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="53" style="2" customWidth="1"/>
-    <col min="11" max="11" width="26.125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="26.1640625" style="2" customWidth="1"/>
     <col min="12" max="12" width="35" style="2" customWidth="1"/>
-    <col min="13" max="13" width="45.625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="45.6640625" style="2" customWidth="1"/>
     <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="18">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2928,7 +2929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -2957,7 +2958,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -2989,7 +2990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>61</v>
       </c>
@@ -3021,7 +3022,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>62</v>
       </c>
@@ -3050,7 +3051,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>63</v>
       </c>
@@ -3079,7 +3080,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>64</v>
       </c>
@@ -3111,7 +3112,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="346.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="360">
       <c r="A8" s="1" t="s">
         <v>65</v>
       </c>
@@ -3144,7 +3145,7 @@
       </c>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="115.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="126">
       <c r="A9" s="1" t="s">
         <v>98</v>
       </c>
@@ -3175,7 +3176,7 @@
       </c>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="90">
       <c r="A10" s="1" t="s">
         <v>99</v>
       </c>
@@ -3209,7 +3210,7 @@
       </c>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="409.6">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -3238,7 +3239,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="247.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="252">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
@@ -3273,7 +3274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="90">
       <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
@@ -3302,7 +3303,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="90">
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
@@ -3331,7 +3332,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="90">
       <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
@@ -3360,7 +3361,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="90">
       <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
@@ -3389,7 +3390,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="90">
       <c r="A17" s="1" t="s">
         <v>37</v>
       </c>
@@ -3418,7 +3419,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="90">
       <c r="A18" s="1" t="s">
         <v>38</v>
       </c>
@@ -3447,7 +3448,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="90">
       <c r="A19" s="1" t="s">
         <v>39</v>
       </c>
@@ -3476,7 +3477,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
@@ -3505,7 +3506,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="409.6">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
@@ -3534,7 +3535,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="90">
       <c r="A22" s="1" t="s">
         <v>110</v>
       </c>
@@ -3569,7 +3570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>111</v>
       </c>
@@ -3601,7 +3602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="90">
       <c r="A24" s="1" t="s">
         <v>42</v>
       </c>
@@ -3633,19 +3634,19 @@
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="E2:E24">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"P4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"P3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"P2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
